--- a/evac_by_zip/evac_by_zip_2026-08-27.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-27.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 212 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 226 addresses (across 3 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
         <v>240</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -948,14 +948,16 @@
       <c r="B13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -1010,52 +1012,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>No named fire</t>
+      <c r="E15" s="7" t="n">
+        <v>231</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
@@ -1063,7 +1065,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>231</v>
+        <v>68</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1072,26 +1074,26 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -1099,7 +1101,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1108,26 +1110,26 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
@@ -1135,7 +1137,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1144,26 +1146,28 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>7</v>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1192,74 +1196,74 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Crook</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>97833</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E21" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -1268,11 +1272,11 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -1285,7 +1289,7 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1294,23 +1298,23 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
@@ -1323,7 +1327,7 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1332,19 +1336,19 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1379,137 +1383,61 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Placed on a ZIP code (table above)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>1452</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>914</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Not placed on any ZIP code (unmatched)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>167</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Placed on a ZIP code (table above)</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>1470</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>916</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Not placed on any ZIP code (unmatched)</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Reconciled total (matches morning report)</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
-        <v>1638</v>
-      </c>
-      <c r="C30" s="18" t="n">
+      <c r="B28" s="18" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C28" s="18" t="n">
         <v>941</v>
       </c>
-      <c r="D30" s="18" t="n">
-        <v>140</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>2719</v>
+      <c r="D28" s="18" t="n">
+        <v>151</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>2711</v>
       </c>
     </row>
   </sheetData>
@@ -1527,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3621,7 +3549,7 @@
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-E</t>
+          <t>US-OR-BAK-SMT-636</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -3641,7 +3569,7 @@
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="G61" s="23" t="n">
@@ -3656,7 +3584,7 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-636</t>
+          <t>US-OR-GRA-GRN-043-E</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -3676,7 +3604,7 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="G62" s="23" t="n">
@@ -6386,7 +6314,7 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1119</t>
+          <t>US-OR-BAK-SMT-636</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
@@ -6406,7 +6334,7 @@
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G140" s="23" t="n">
@@ -6414,38 +6342,38 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="23" t="inlineStr">
+      <c r="A141" s="25" t="inlineStr">
         <is>
           <t>97814</t>
         </is>
       </c>
-      <c r="B141" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C141" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D141" s="24" t="inlineStr">
+      <c r="B141" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1252</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D141" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E141" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F141" s="23" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="n">
-        <v>1</v>
+      <c r="E141" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F141" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G141" s="25" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="142">
@@ -6456,7 +6384,7 @@
       </c>
       <c r="B142" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1252</t>
+          <t>US-OR-BAK-SMT-610</t>
         </is>
       </c>
       <c r="C142" s="26" t="inlineStr">
@@ -6476,11 +6404,11 @@
       </c>
       <c r="F142" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G142" s="25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -6491,7 +6419,7 @@
       </c>
       <c r="B143" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-610</t>
+          <t>US-OR-BAK-SMT-600</t>
         </is>
       </c>
       <c r="C143" s="26" t="inlineStr">
@@ -6526,7 +6454,7 @@
       </c>
       <c r="B144" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-600</t>
+          <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
       <c r="C144" s="26" t="inlineStr">
@@ -6546,7 +6474,7 @@
       </c>
       <c r="F144" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G144" s="25" t="n">
@@ -6554,224 +6482,224 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B145" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1242</t>
-        </is>
-      </c>
-      <c r="C145" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D145" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E145" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F145" s="25" t="inlineStr">
+      <c r="A145" s="21" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C145" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E145" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G145" s="21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="25" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B146" s="26" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="C146" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D146" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E146" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F146" s="25" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="G146" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="inlineStr">
+        <is>
+          <t>97063</t>
+        </is>
+      </c>
+      <c r="B147" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D147" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E147" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G147" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="25" t="inlineStr">
+        <is>
+          <t>97063</t>
+        </is>
+      </c>
+      <c r="B148" s="26" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="C148" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D148" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E148" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F148" s="25" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G145" s="25" t="n">
+      <c r="G148" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="21" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B146" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C149" s="24" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D146" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E146" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F146" s="21" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G146" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="25" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B147" s="26" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C147" s="26" t="inlineStr">
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E149" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F149" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C150" s="24" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D147" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E147" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F147" s="25" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="G147" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B148" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E148" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F148" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G148" s="21" t="n">
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F150" s="23" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G150" s="23" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="25" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B149" s="26" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C149" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D149" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E149" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F149" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G149" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="21" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B150" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C150" s="22" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D150" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E150" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F150" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G150" s="21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="25" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B151" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>Cooper Spur North</t>
         </is>
       </c>
       <c r="C151" s="26" t="inlineStr">
@@ -6781,7 +6709,7 @@
       </c>
       <c r="D151" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E151" s="25" t="inlineStr">
@@ -6791,81 +6719,81 @@
       </c>
       <c r="F151" s="25" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="G151" s="25" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="23" t="inlineStr">
+      <c r="A152" s="25" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B152" s="24" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C152" s="24" t="inlineStr">
+      <c r="B152" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C152" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D152" s="24" t="inlineStr">
+      <c r="D152" s="26" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E152" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F152" s="23" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
+      <c r="E152" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F152" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G152" s="25" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B153" s="26" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C153" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D153" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E153" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F153" s="25" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G153" s="25" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B153" s="24" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C153" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D153" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E153" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F153" s="23" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -6876,7 +6804,7 @@
       </c>
       <c r="B154" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C154" s="26" t="inlineStr">
@@ -6896,102 +6824,102 @@
       </c>
       <c r="F154" s="25" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G154" s="25" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B155" s="26" t="inlineStr">
-        <is>
-          <t>Cooper Spur South</t>
-        </is>
-      </c>
-      <c r="C155" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D155" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E155" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F155" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G155" s="25" t="n">
-        <v>63</v>
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C155" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D155" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B156" s="26" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C156" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D156" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E156" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F156" s="25" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G156" s="25" t="n">
-        <v>4</v>
+      <c r="A156" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B156" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1450</t>
+        </is>
+      </c>
+      <c r="C156" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D156" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E156" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G156" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="25" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B157" s="26" t="inlineStr">
         <is>
-          <t>White River</t>
+          <t>US-OR-UNI-UCO-1421</t>
         </is>
       </c>
       <c r="C157" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D157" s="26" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E157" s="25" t="inlineStr">
@@ -7001,81 +6929,81 @@
       </c>
       <c r="F157" s="25" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G157" s="25" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="23" t="inlineStr">
+      <c r="A158" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B158" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1435</t>
-        </is>
-      </c>
-      <c r="C158" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D158" s="24" t="inlineStr">
+      <c r="B158" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1436</t>
+        </is>
+      </c>
+      <c r="C158" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D158" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E158" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F158" s="23" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="n">
-        <v>6</v>
+      <c r="E158" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F158" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G158" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="23" t="inlineStr">
+      <c r="A159" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B159" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C159" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D159" s="24" t="inlineStr">
+      <c r="B159" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1437</t>
+        </is>
+      </c>
+      <c r="C159" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D159" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E159" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F159" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="n">
-        <v>1</v>
+      <c r="E159" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F159" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G159" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -7086,7 +7014,7 @@
       </c>
       <c r="B160" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C160" s="26" t="inlineStr">
@@ -7106,67 +7034,67 @@
       </c>
       <c r="F160" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G160" s="25" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B161" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1436</t>
-        </is>
-      </c>
-      <c r="C161" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D161" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E161" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F161" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G161" s="25" t="n">
-        <v>9</v>
+      <c r="A161" s="23" t="inlineStr">
+        <is>
+          <t>97603</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1941</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E161" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F161" s="23" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B162" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-KLA-KLA-2261</t>
         </is>
       </c>
       <c r="C162" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D162" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E162" s="25" t="inlineStr">
@@ -7176,32 +7104,32 @@
       </c>
       <c r="F162" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G162" s="25" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B163" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1438</t>
+          <t>US-OR-KLA-KLA-1936</t>
         </is>
       </c>
       <c r="C163" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D163" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E163" s="25" t="inlineStr">
@@ -7211,46 +7139,46 @@
       </c>
       <c r="F163" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G163" s="25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="23" t="inlineStr">
+      <c r="A164" s="25" t="inlineStr">
         <is>
           <t>97603</t>
         </is>
       </c>
-      <c r="B164" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C164" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D164" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E164" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F164" s="23" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="n">
-        <v>15</v>
+      <c r="B164" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2256</t>
+        </is>
+      </c>
+      <c r="C164" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D164" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E164" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F164" s="25" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G164" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -7261,7 +7189,7 @@
       </c>
       <c r="B165" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C165" s="26" t="inlineStr">
@@ -7281,11 +7209,11 @@
       </c>
       <c r="F165" s="25" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G165" s="25" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -7296,7 +7224,7 @@
       </c>
       <c r="B166" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1936</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C166" s="26" t="inlineStr">
@@ -7316,102 +7244,102 @@
       </c>
       <c r="F166" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G166" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B167" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-2256</t>
-        </is>
-      </c>
-      <c r="C167" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D167" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E167" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F167" s="25" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="G167" s="25" t="n">
-        <v>1</v>
+      <c r="A167" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B167" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C167" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D167" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F167" s="23" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="25" t="inlineStr">
-        <is>
-          <t>97603</t>
-        </is>
-      </c>
-      <c r="B168" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C168" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D168" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E168" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F168" s="25" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G168" s="25" t="n">
+      <c r="A168" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-121-B</t>
+        </is>
+      </c>
+      <c r="C168" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F168" s="23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="25" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B169" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-UMA-UMC-032</t>
         </is>
       </c>
       <c r="C169" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D169" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E169" s="25" t="inlineStr">
@@ -7421,137 +7349,137 @@
       </c>
       <c r="F169" s="25" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G169" s="25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B170" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-123-B</t>
+        </is>
+      </c>
+      <c r="C170" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D170" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E170" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F170" s="25" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="G170" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="23" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="25" t="inlineStr">
         <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B170" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C170" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D170" s="24" t="inlineStr">
+      <c r="B171" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406025-B</t>
+        </is>
+      </c>
+      <c r="C171" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D171" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E170" s="23" t="inlineStr">
+      <c r="E171" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F171" s="25" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G171" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="23" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C172" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E172" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F170" s="23" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="G170" s="23" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B171" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C171" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D171" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E171" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F171" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="n">
+      <c r="F172" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G172" s="23" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B172" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C172" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D172" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E172" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F172" s="25" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G172" s="25" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B173" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-123-B</t>
+          <t>US-OR-CRO-CRR-8SB</t>
         </is>
       </c>
       <c r="C173" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D173" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook</t>
         </is>
       </c>
       <c r="E173" s="25" t="inlineStr">
@@ -7561,32 +7489,32 @@
       </c>
       <c r="F173" s="25" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="G173" s="25" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B174" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
+          <t>US-OR-CRO-CRR-4SC</t>
         </is>
       </c>
       <c r="C174" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D174" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Crook</t>
         </is>
       </c>
       <c r="E174" s="25" t="inlineStr">
@@ -7596,46 +7524,46 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G174" s="25" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="23" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B175" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1119</t>
-        </is>
-      </c>
-      <c r="C175" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D175" s="24" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E175" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F175" s="23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G175" s="23" t="n">
-        <v>1</v>
+      <c r="A175" s="25" t="inlineStr">
+        <is>
+          <t>97754</t>
+        </is>
+      </c>
+      <c r="B175" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4SK-A</t>
+        </is>
+      </c>
+      <c r="C175" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D175" s="26" t="inlineStr">
+        <is>
+          <t>Crook</t>
+        </is>
+      </c>
+      <c r="E175" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F175" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G175" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -7709,59 +7637,59 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="23" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B178" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C178" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D178" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E178" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F178" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G178" s="23" t="n">
-        <v>1</v>
+      <c r="A178" s="25" t="inlineStr">
+        <is>
+          <t>97037</t>
+        </is>
+      </c>
+      <c r="B178" s="26" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+      <c r="C178" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D178" s="26" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E178" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F178" s="25" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G178" s="25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B179" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SB</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C179" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D179" s="26" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E179" s="25" t="inlineStr">
@@ -7771,32 +7699,32 @@
       </c>
       <c r="F179" s="25" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G179" s="25" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B180" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C180" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D180" s="26" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E180" s="25" t="inlineStr">
@@ -7806,32 +7734,32 @@
       </c>
       <c r="F180" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G180" s="25" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B181" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C181" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D181" s="26" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E181" s="25" t="inlineStr">
@@ -7841,32 +7769,32 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G181" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="25" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B182" s="26" t="inlineStr">
         <is>
-          <t>BC1</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C182" s="26" t="inlineStr">
         <is>
-          <t>Burnt Creek Fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D182" s="26" t="inlineStr">
         <is>
-          <t>Wallowa</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E182" s="25" t="inlineStr">
@@ -7876,32 +7804,32 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G182" s="25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="25" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="B183" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>US-OR-KLA-KLA-1931</t>
         </is>
       </c>
       <c r="C183" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E183" s="25" t="inlineStr">
@@ -7911,190 +7839,15 @@
       </c>
       <c r="F183" s="25" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G183" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="25" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B184" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1572</t>
-        </is>
-      </c>
-      <c r="C184" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D184" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E184" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F184" s="25" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="G184" s="25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="25" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B185" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1566</t>
-        </is>
-      </c>
-      <c r="C185" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D185" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E185" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F185" s="25" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G185" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="25" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B186" s="26" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C186" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D186" s="26" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E186" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F186" s="25" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G186" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B187" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C187" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D187" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E187" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F187" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G187" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="25" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="B188" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1931</t>
-        </is>
-      </c>
-      <c r="C188" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D188" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E188" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F188" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G188" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" s="27" t="inlineStr">
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -8102,7 +7855,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A190:G190"/>
+    <mergeCell ref="A185:G185"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
